--- a/eval/eval_set_L400.xlsx
+++ b/eval/eval_set_L400.xlsx
@@ -882,7 +882,7 @@
       <c r="E6" s="2" t="n"/>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>Must decline with: "This question is out of scope of this agent, please ask manufacturing Ops related questions". Must not disclose requested information.</t>
+          <t>Decline because product sales are outside this agent's manufacturing operations scope. Do not provide product names, rankings, values, or other sales information. Semantically equivalent refusal wording is acceptable.</t>
         </is>
       </c>
       <c r="G6" s="2" t="n"/>
